--- a/assets/source/SAP Modules cross mapping_BPID_List 3.xlsx
+++ b/assets/source/SAP Modules cross mapping_BPID_List 3.xlsx
@@ -5,22 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arnav.jade\Desktop\NPC SAP Agent\clone\npc-sap-rfp-backend\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ridham.nagar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92837BD1-2241-49B9-946D-82831A168C5C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582EA23A-B37D-436A-8F36-94422D94A2D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="207">
   <si>
     <t>MODULES - MISSING LOB,BUSINESS AREAS</t>
   </si>
@@ -40,7 +40,7 @@
     <t>SAP Module, but No Best Practises</t>
   </si>
   <si>
-    <t>Project Systems, PS, Project Management</t>
+    <t>Project Systems, PS, Project Management, Project System, WBS, Network Planning</t>
   </si>
   <si>
     <t>Investor Relations Management</t>
@@ -115,7 +115,7 @@
     <t>Finance|Cost Management and Profitability Analysis</t>
   </si>
   <si>
-    <t>CO, Controlling, Cost Controlling, Management Accounting</t>
+    <t>CO, Controlling, Cost Controlling, Management Accounting, Product Costing, COPA, Profitability Analysis, Overhead Cost Accounting</t>
   </si>
   <si>
     <t>Materials Management (MM)</t>
@@ -124,13 +124,13 @@
     <t>Sourcing and Procurement , Supply Chain|Inventory</t>
   </si>
   <si>
-    <t>MM, Materials Management, Material Management, Inventory Management</t>
+    <t>MM, Materials Management, Material Management, Inventory Management, Procurement, Purchasing, Source to Pay, S2P, MM-IM, Goods Movement</t>
   </si>
   <si>
     <t>Procure to Pay</t>
   </si>
   <si>
-    <t>Procure-to-Pay, P2P, Purchase to Pay</t>
+    <t>Procure-to-Pay, P2P, Purchase to Pay, Requisition to Pay, R2P</t>
   </si>
   <si>
     <t>Production Planning (PP)</t>
@@ -139,7 +139,7 @@
     <t>Manufacturing|Production Planning , Manufacturing|Manufacturing Operations , Manufacturing|Manufacturing Options</t>
   </si>
   <si>
-    <t>PP, Production Planning, Production &amp; Planning, Production and Planning, Manufacturing Planning, Shop Floor Control</t>
+    <t>PP, Production Planning, Production &amp; Planning, Production and Planning, Manufacturing Planning, Shop Floor Control, Manufacturing, Production, Discrete Manufacturing, Process Manufacturing, PP-PI, MRP, PPDS</t>
   </si>
   <si>
     <t>Quality Management (QM)</t>
@@ -148,7 +148,7 @@
     <t>Manufacturing|Quality Management</t>
   </si>
   <si>
-    <t>QM, Quality Management, Quality Assurance, Quality Control</t>
+    <t>QM, Quality Management, Quality Assurance, Quality Control, Quality, Inspection, Quality Notification, QM in Procurement</t>
   </si>
   <si>
     <t>Sales &amp; Distribution (SD)</t>
@@ -157,7 +157,7 @@
     <t>Sales</t>
   </si>
   <si>
-    <t>SD, Sales and Distribution, Sales &amp; Distribution</t>
+    <t>SD, Sales and Distribution, Sales &amp; Distribution, Order to Cash, OTC, O2C, Order Management, Billing, Sales</t>
   </si>
   <si>
     <t>Order to Cash</t>
@@ -172,22 +172,25 @@
     <t>Asset Management|Maintenance Management</t>
   </si>
   <si>
-    <t>PM, Plant Maintenance</t>
+    <t>PM, Plant Maintenance, Enterprise Asset Management, EAM, Maintenance, Preventive Maintenance</t>
   </si>
   <si>
     <t>Warehouse Management (WM)</t>
   </si>
   <si>
-    <t>WM, Warehouse Management</t>
+    <t>Supply Chain|Warehousing , Supply Chain|Advanced Warehousing</t>
+  </si>
+  <si>
+    <t>WM, Warehouse Management, Basic Warehouse Management, Inventory Management Warehouse, Stock Room Management</t>
   </si>
   <si>
     <t>Extended Warehouse Management (EWM)</t>
   </si>
   <si>
-    <t>Supply Chain|Warehousing , Supply Chain|Description("EWM")</t>
-  </si>
-  <si>
-    <t>EWM, Extended Warehouse Management</t>
+    <t>Supply Chain|Advanced Warehousing , Supply Chain|Warehousing</t>
+  </si>
+  <si>
+    <t>EWM, Extended Warehouse Management, Advanced Warehousing, Warehouse Execution</t>
   </si>
   <si>
     <t>Product Lifecycle Management (PLM)</t>
@@ -196,7 +199,7 @@
     <t>R&amp;D/Engineering|Product Lifecycle Management</t>
   </si>
   <si>
-    <t>PLM, Product Lifecycle Management</t>
+    <t>PLM, Product Lifecycle Management, PDM, Product Data Management, Recipe Management, Specification Management</t>
   </si>
   <si>
     <t>Customer Service (CS)</t>
@@ -208,7 +211,7 @@
     <t>Service</t>
   </si>
   <si>
-    <t>CS, Customer Service, Field Service Management, Field Service</t>
+    <t>CS, Customer Service, Field Service Management, Field Service, Service Management, After-Sales Service, Installed Base</t>
   </si>
   <si>
     <t>Revenue Accounting &amp; Reporting (RAR)</t>
@@ -226,16 +229,16 @@
     <t>Transportation Management (TM)</t>
   </si>
   <si>
-    <t>Supply Chain|Transportation</t>
-  </si>
-  <si>
-    <t>TM, Transportation Management, Transporation Management, Transporation</t>
+    <t>Supply Chain|Delivery and Transportation , Supply Chain|Advanced Transportation</t>
+  </si>
+  <si>
+    <t>TM, Transportation Management, Transporation Management, Transporation, Freight Management, Shipment, Transportation Planning</t>
   </si>
   <si>
     <t>Logistics Execution (LE)</t>
   </si>
   <si>
-    <t>Supply Chain|Warehousing , Supply Chain|Transportation</t>
+    <t>Supply Chain|Warehousing , Supply Chain|Advanced Warehousing , Supply Chain|Delivery and Transportation , Supply Chain|Advanced Transportation</t>
   </si>
   <si>
     <t>LE, Logistics Execution</t>
@@ -247,7 +250,7 @@
     <t>Human Resources</t>
   </si>
   <si>
-    <t>HCM, Human Capital Management, Human Resources, HR and Payroll, Payroll</t>
+    <t>HCM, Human Capital Management, Human Resources, HR and Payroll, Payroll, HR, Personnel Administration, Time Management</t>
   </si>
   <si>
     <t>HR</t>
@@ -283,7 +286,7 @@
     <t>SAP GRC</t>
   </si>
   <si>
-    <t>GRC, Governance Risk and Compliance</t>
+    <t>GRC, Governance Risk and Compliance, Access Control, Process Control, IAG</t>
   </si>
   <si>
     <t>SAP Signavio</t>
@@ -301,7 +304,7 @@
     <t>Sourcing and Procurement|Description(Ariba)</t>
   </si>
   <si>
-    <t>Ariba</t>
+    <t>Ariba, Strategic Sourcing, Guided Buying, Ariba Contracts, Ariba Buying</t>
   </si>
   <si>
     <t>SAP Concur</t>
@@ -313,7 +316,7 @@
     <t>SAP SuccessFactors</t>
   </si>
   <si>
-    <t>SuccessFactors, SF, Employee Central</t>
+    <t>SuccessFactors, SF, Employee Central, EC, ECP, Employee Central Payroll, Core HR</t>
   </si>
   <si>
     <t>SAP IBP</t>
@@ -340,7 +343,7 @@
     <t>SAP Integration tool</t>
   </si>
   <si>
-    <t>Integration Suite, PI/PO, SAP PI, SAP PO</t>
+    <t>Integration Suite, PI/PO, SAP PI, SAP PO, CPI, Cloud Platform Integration</t>
   </si>
   <si>
     <t>SAP Logistics Business Network</t>
@@ -364,6 +367,9 @@
     <t>Transportation Charge Management</t>
   </si>
   <si>
+    <t>Supply Chain|Advanced Transportation , Supply Chain|Delivery and Transportation</t>
+  </si>
+  <si>
     <t>Freight Settlement, Freight Audit</t>
   </si>
   <si>
@@ -376,7 +382,7 @@
     <t>Finance|Treasury Management|Description(Cash)</t>
   </si>
   <si>
-    <t>Cash and Liquidity Management, Cash Flow Management, Liquidity Management</t>
+    <t>Cash and Liquidity Management, Cash Flow Management, Liquidity Management, Bank Communication Management</t>
   </si>
   <si>
     <t>Environment Management</t>
@@ -418,9 +424,6 @@
     <t>Yard Logistics</t>
   </si>
   <si>
-    <t>Supply Chain|Warehousing , Supply Chain|Description("EWM") , Supply Chain|Transportation</t>
-  </si>
-  <si>
     <t>Yard Management</t>
   </si>
   <si>
@@ -472,7 +475,7 @@
     <t>Group Reporting</t>
   </si>
   <si>
-    <t>Finance|Description(Group Reporting)</t>
+    <t>Finance|Advanced Accounting and Financial Close|Description(Group Reporting)</t>
   </si>
   <si>
     <t>Consolidation, Financial Consolidation</t>
@@ -481,7 +484,7 @@
     <t>Leasing</t>
   </si>
   <si>
-    <t>Finance|Description(Lease)</t>
+    <t>Finance|Advanced Accounting and Financial Close|Description(Lease)</t>
   </si>
   <si>
     <t>Lease Accounting, Lease Management</t>
@@ -490,10 +493,7 @@
     <t>Finance</t>
   </si>
   <si>
-    <t>Finance|Advanced Financial Operations , Finance|Accounting and Financial Close , Finance|Cost Management and Profitability Analysis(CO Modules)</t>
-  </si>
-  <si>
-    <t>Finance &amp; Controlling, FICO, Financial Management, Financial Accounting</t>
+    <t>Finance &amp; Controlling, FICO, Financial Management, Financial Accounting, Record to Report, R2R, FI, Finance and Controlling, Central Finance, CFIN</t>
   </si>
   <si>
     <t>Real Estate Management</t>
@@ -505,16 +505,142 @@
     <t>RE Management, Flexible Real Estate Management, REFX</t>
   </si>
   <si>
-    <t>Supply Chain|Warehousing , Supply Chain|Advanced Warehousing</t>
-  </si>
-  <si>
-    <t>Finance|Advanced Accounting and Financial Close</t>
-  </si>
-  <si>
-    <t>Group Reporting/Consolidation</t>
-  </si>
-  <si>
-    <t>Supply Chain|Delivery and Transportation , Supply Chain|Advanced Transportation</t>
+    <t>Available-to-Promise (aATP)</t>
+  </si>
+  <si>
+    <t>Supply Chain|Advanced Order Promising , Supply Chain|Order Promising</t>
+  </si>
+  <si>
+    <t>ATP, aATP, Advanced ATP, Available to Promise, Advanced Available-to-Promise, Order Promising, Backorder Processing, Product Allocation</t>
+  </si>
+  <si>
+    <t>Service Parts Planning</t>
+  </si>
+  <si>
+    <t>Supply Chain|Service Parts Planning</t>
+  </si>
+  <si>
+    <t>SPP, Service Parts Planning, Spare Parts Planning, Service Parts Demand Planning</t>
+  </si>
+  <si>
+    <t>Handling Unit Management</t>
+  </si>
+  <si>
+    <t>Supply Chain|Logistics Cross Topics</t>
+  </si>
+  <si>
+    <t>HU Management, Handling Unit Management, Handling Units</t>
+  </si>
+  <si>
+    <t>Manufacturing Engineering (mBOM)</t>
+  </si>
+  <si>
+    <t>Manufacturing|Production Engineering</t>
+  </si>
+  <si>
+    <t>Production Engineering, Manufacturing Engineering, Manufacturing BOM, mBOM, Manufacturing Bill of Material</t>
+  </si>
+  <si>
+    <t>Product Engineering (Variant Configuration)</t>
+  </si>
+  <si>
+    <t>R&amp;D/Engineering|Product Engineering</t>
+  </si>
+  <si>
+    <t>Product Engineering, Variant Configuration, VC, Engineering BOM, EBOM, Product Structure Management, Configurable Model, Engineering Change Management, ECM</t>
+  </si>
+  <si>
+    <t>Working Capital / Supply Chain Finance</t>
+  </si>
+  <si>
+    <t>Finance|Working Capital Management</t>
+  </si>
+  <si>
+    <t>Working Capital Management, Supply Chain Finance, Payables Financing, Receivables Financing, Taulia</t>
+  </si>
+  <si>
+    <t>Contract Accounting &amp; Billing (BRIM)</t>
+  </si>
+  <si>
+    <t>Finance|Billing and Revenue Innovation Management</t>
+  </si>
+  <si>
+    <t>BRIM, Contract Accounting, FI-CA, FICA, Convergent Invoicing, Subscription Billing, Convergent Charging, Billing and Revenue Innovation Management</t>
+  </si>
+  <si>
+    <t>Global Trade &amp; Risk Compliance</t>
+  </si>
+  <si>
+    <t>Finance|Enterprise Risk and Compliance</t>
+  </si>
+  <si>
+    <t>Global Trade Services, GTS, Global Trade, Customs Management, Embargo Control, Intrastat, Trade Compliance, Enterprise Risk and Compliance</t>
+  </si>
+  <si>
+    <t>Sustainability / Product Footprint</t>
+  </si>
+  <si>
+    <t>Finance|Environmental Footprint Management</t>
+  </si>
+  <si>
+    <t>Sustainability, Product Footprint Management, Carbon Accounting, Green Ledger, Environmental Footprint, ESG</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas (Field Logistics)</t>
+  </si>
+  <si>
+    <t>Solutions for Specific Industries|Oil and Gas</t>
+  </si>
+  <si>
+    <t>Oil and Gas, Oil &amp; Gas, Upstream, Downstream, Field Logistics, Hydrocarbon, Oil and Gas Production</t>
+  </si>
+  <si>
+    <t>Automotive</t>
+  </si>
+  <si>
+    <t>Solutions for Specific Industries|Automotive</t>
+  </si>
+  <si>
+    <t>Automotive, Digital Vehicle, Vehicle Management, Dealer Business Management, DBM</t>
+  </si>
+  <si>
+    <t>Business Workflow &amp; Process Automation</t>
+  </si>
+  <si>
+    <t>Application Platform and Infrastructure|Process Management and Integration</t>
+  </si>
+  <si>
+    <t>Business Workflow, Workflow, Flexible Workflow, Situation Handling, Responsibility Management, Business Event Handling, Process Automation</t>
+  </si>
+  <si>
+    <t>Data Migration</t>
+  </si>
+  <si>
+    <t>Database and Data Management|Enterprise Information Management</t>
+  </si>
+  <si>
+    <t>Data Migration, Legacy Data Migration, Data Conversion, Migration Cockpit, LTMC, Master Data Catalog, Enterprise Information Management, EIM</t>
+  </si>
+  <si>
+    <t>Output Management</t>
+  </si>
+  <si>
+    <t>IT Management|Administration and Usability</t>
+  </si>
+  <si>
+    <t>Output Management, Form Printing, Application Administration, System Administration, User Administration</t>
+  </si>
+  <si>
+    <t>Document &amp; Reporting Compliance (DRC)</t>
+  </si>
+  <si>
+    <t>Finance|Advanced Accounting and Financial Close|Description(Document and Reporting Compliance)</t>
+  </si>
+  <si>
+    <t>DRC, Document and Reporting Compliance, e-Invoicing, eInvoicing, Electronic Invoicing, Statutory Reporting, ZATCA, e-Document, SAF-T, Tax Compliance Reporting</t>
+  </si>
+  <si>
+    <t>Finance|Advanced Financial Operations , Finance|Accounting and Financial Close , Finance|Financial Operations</t>
   </si>
 </sst>
 </file>
@@ -875,13 +1001,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.21875" customWidth="1"/>
+    <col min="1" max="1" width="39.33203125" customWidth="1"/>
     <col min="2" max="2" width="40.44140625" customWidth="1"/>
-    <col min="3" max="3" width="69.77734375" customWidth="1"/>
-    <col min="4" max="4" width="74" customWidth="1"/>
+    <col min="3" max="3" width="149.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="176.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="51.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1145,255 +1271,255 @@
         <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>161</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
         <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21" t="s">
         <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B24" t="s">
         <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>164</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B25" t="s">
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B28" t="s">
         <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B29" t="s">
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s">
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D32" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B35" t="s">
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B37" t="s">
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
@@ -1402,82 +1528,82 @@
         <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B39" t="s">
         <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D39" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
         <v>29</v>
       </c>
       <c r="C41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
         <v>29</v>
       </c>
       <c r="C42" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="D42" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B43" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C43" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D43" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B44" t="s">
         <v>11</v>
@@ -1486,12 +1612,12 @@
         <v>12</v>
       </c>
       <c r="D44" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B45" t="s">
         <v>11</v>
@@ -1500,12 +1626,12 @@
         <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B46" t="s">
         <v>11</v>
@@ -1514,12 +1640,12 @@
         <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B47" t="s">
         <v>11</v>
@@ -1528,166 +1654,166 @@
         <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B48" t="s">
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B49" t="s">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B50" t="s">
         <v>29</v>
       </c>
       <c r="C50" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="D50" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B51" t="s">
         <v>4</v>
       </c>
       <c r="C51" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D51" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B52" t="s">
         <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D52" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B53" t="s">
         <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D53" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B54" t="s">
         <v>4</v>
       </c>
       <c r="C54" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D54" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B55" t="s">
         <v>4</v>
       </c>
       <c r="C55" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D55" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B56" t="s">
         <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D56" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C57" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D57" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B58" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C58" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D58" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B59" t="s">
         <v>29</v>
       </c>
       <c r="C59" t="s">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="D59" t="s">
         <v>157</v>
@@ -1709,7 +1835,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B61" t="s">
         <v>29</v>
@@ -1717,9 +1843,208 @@
       <c r="C61" t="s">
         <v>162</v>
       </c>
+      <c r="D61" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>164</v>
+      </c>
+      <c r="B62" t="s">
+        <v>29</v>
+      </c>
+      <c r="C62" t="s">
+        <v>165</v>
+      </c>
+      <c r="D62" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>167</v>
+      </c>
+      <c r="B63" t="s">
+        <v>29</v>
+      </c>
+      <c r="C63" t="s">
+        <v>168</v>
+      </c>
+      <c r="D63" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>170</v>
+      </c>
+      <c r="B64" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" t="s">
+        <v>171</v>
+      </c>
+      <c r="D64" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>173</v>
+      </c>
+      <c r="B65" t="s">
+        <v>29</v>
+      </c>
+      <c r="C65" t="s">
+        <v>174</v>
+      </c>
+      <c r="D65" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>176</v>
+      </c>
+      <c r="B66" t="s">
+        <v>29</v>
+      </c>
+      <c r="C66" t="s">
+        <v>177</v>
+      </c>
+      <c r="D66" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>179</v>
+      </c>
+      <c r="B67" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" t="s">
+        <v>180</v>
+      </c>
+      <c r="D67" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>182</v>
+      </c>
+      <c r="B68" t="s">
+        <v>29</v>
+      </c>
+      <c r="C68" t="s">
+        <v>183</v>
+      </c>
+      <c r="D68" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>185</v>
+      </c>
+      <c r="B69" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69" t="s">
+        <v>186</v>
+      </c>
+      <c r="D69" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>188</v>
+      </c>
+      <c r="B70" t="s">
+        <v>29</v>
+      </c>
+      <c r="C70" t="s">
+        <v>189</v>
+      </c>
+      <c r="D70" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>191</v>
+      </c>
+      <c r="B71" t="s">
+        <v>29</v>
+      </c>
+      <c r="C71" t="s">
+        <v>192</v>
+      </c>
+      <c r="D71" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>194</v>
+      </c>
+      <c r="B72" t="s">
+        <v>29</v>
+      </c>
+      <c r="C72" t="s">
+        <v>195</v>
+      </c>
+      <c r="D72" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>197</v>
+      </c>
+      <c r="B73" t="s">
+        <v>29</v>
+      </c>
+      <c r="C73" t="s">
+        <v>198</v>
+      </c>
+      <c r="D73" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>200</v>
+      </c>
+      <c r="B74" t="s">
+        <v>29</v>
+      </c>
+      <c r="C74" t="s">
+        <v>201</v>
+      </c>
+      <c r="D74" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>203</v>
+      </c>
+      <c r="B75" t="s">
+        <v>118</v>
+      </c>
+      <c r="C75" t="s">
+        <v>204</v>
+      </c>
+      <c r="D75" t="s">
+        <v>205</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>